--- a/fileTemplates/studentTemplates/blockApplicantTemplate(XLSX).xlsx
+++ b/fileTemplates/studentTemplates/blockApplicantTemplate(XLSX).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Programming\VSCode\CAPSTONE-preEnrollment\preEnrollmentV9.1\fileTemplates\studentTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152C0A49-D460-4151-B2FD-682B85D8E0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1A8BCF-6693-4271-BADA-8D236CED8A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6741A616-476E-4690-9F1F-0845B32B7F60}"/>
   </bookViews>
@@ -247,7 +247,7 @@
     <t>Jr.</t>
   </si>
   <si>
-    <t>A-202610127</t>
+    <t>A-202610128</t>
   </si>
 </sst>
 </file>

--- a/fileTemplates/studentTemplates/blockApplicantTemplate(XLSX).xlsx
+++ b/fileTemplates/studentTemplates/blockApplicantTemplate(XLSX).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Programming\VSCode\CAPSTONE-preEnrollment\preEnrollmentV9.1\fileTemplates\studentTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1A8BCF-6693-4271-BADA-8D236CED8A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A274CC0E-D577-4123-88DC-6522A8E994D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6741A616-476E-4690-9F1F-0845B32B7F60}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="108">
   <si>
     <t>firstName</t>
   </si>
@@ -187,9 +187,6 @@
     <t>Asawa</t>
   </si>
   <si>
-    <t>truo</t>
-  </si>
-  <si>
     <t>Sipat</t>
   </si>
   <si>
@@ -223,38 +220,137 @@
     <t>applicantID</t>
   </si>
   <si>
-    <t>A-202610129</t>
-  </si>
-  <si>
-    <t>Alonso</t>
-  </si>
-  <si>
-    <t>Calme</t>
-  </si>
-  <si>
-    <t>Kenoki</t>
-  </si>
-  <si>
-    <t>Aliser</t>
-  </si>
-  <si>
-    <t>Omipa</t>
-  </si>
-  <si>
-    <t>Culden</t>
-  </si>
-  <si>
-    <t>Jr.</t>
-  </si>
-  <si>
-    <t>A-202610128</t>
+    <t>Kanto</t>
+  </si>
+  <si>
+    <t>kanto</t>
+  </si>
+  <si>
+    <t>A-201736341</t>
+  </si>
+  <si>
+    <t>A-201736342</t>
+  </si>
+  <si>
+    <t>A-201736343</t>
+  </si>
+  <si>
+    <t>A-201736344</t>
+  </si>
+  <si>
+    <t>A-201736345</t>
+  </si>
+  <si>
+    <t>A-201736346</t>
+  </si>
+  <si>
+    <t>A-201736347</t>
+  </si>
+  <si>
+    <t>A-201736348</t>
+  </si>
+  <si>
+    <t>A-201736349</t>
+  </si>
+  <si>
+    <t>A-201736350</t>
+  </si>
+  <si>
+    <t>Dave</t>
+  </si>
+  <si>
+    <t>Planto</t>
+  </si>
+  <si>
+    <t>Halaman</t>
+  </si>
+  <si>
+    <t>Oratio</t>
+  </si>
+  <si>
+    <t>Nunez</t>
+  </si>
+  <si>
+    <t>Wagamo</t>
+  </si>
+  <si>
+    <t>Wakami</t>
+  </si>
+  <si>
+    <t>Lakon</t>
+  </si>
+  <si>
+    <t>Ochiba</t>
+  </si>
+  <si>
+    <t>Dantan Lei </t>
+  </si>
+  <si>
+    <t>Coral </t>
+  </si>
+  <si>
+    <t>Lanaria</t>
+  </si>
+  <si>
+    <t>Haluno</t>
+  </si>
+  <si>
+    <t>Aton </t>
+  </si>
+  <si>
+    <t>Mutto</t>
+  </si>
+  <si>
+    <t>Persimon </t>
+  </si>
+  <si>
+    <t>Artu</t>
+  </si>
+  <si>
+    <t>La Manda</t>
+  </si>
+  <si>
+    <t>Kataria </t>
+  </si>
+  <si>
+    <t>Jafar</t>
+  </si>
+  <si>
+    <t>Alaam </t>
+  </si>
+  <si>
+    <t>Rando</t>
+  </si>
+  <si>
+    <t>Sweep</t>
+  </si>
+  <si>
+    <t>Takes</t>
+  </si>
+  <si>
+    <t>Harlan Jon</t>
+  </si>
+  <si>
+    <t>Manlo</t>
+  </si>
+  <si>
+    <t>Earnu</t>
+  </si>
+  <si>
+    <t>Hai Pang</t>
+  </si>
+  <si>
+    <t>Koi</t>
+  </si>
+  <si>
+    <t>Chutek</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -385,6 +481,12 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1123,7 +1225,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD90307F-AAA9-4EEF-AA9C-646331FFAE3B}">
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
@@ -1179,7 +1281,7 @@
   <sheetData>
     <row r="1" spans="1:50" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -1331,22 +1433,19 @@
     </row>
     <row r="2" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F2" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>49</v>
@@ -1376,16 +1475,16 @@
         <v>777</v>
       </c>
       <c r="P2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="T2" s="1">
         <v>3002</v>
@@ -1394,76 +1493,76 @@
         <v>777</v>
       </c>
       <c r="V2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="W2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="Z2" s="1">
         <v>3002</v>
       </c>
       <c r="AA2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="AC2" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AB2" s="1">
-        <v>9123356789</v>
-      </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AD2" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="AE2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AD2" s="1">
-        <v>9123356789</v>
-      </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AG2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AG2" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="AH2" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AJ2" s="1">
         <v>2007</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AM2" s="1">
         <v>2007</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AP2" s="1">
         <v>2005</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AR2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AS2" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AT2" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="AS2" s="1">
-        <v>2007</v>
-      </c>
-      <c r="AT2" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="AU2" s="1" t="b">
         <v>1</v>
@@ -1480,19 +1579,19 @@
     </row>
     <row r="3" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="F3" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>49</v>
@@ -1522,16 +1621,16 @@
         <v>777</v>
       </c>
       <c r="P3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="T3" s="1">
         <v>3002</v>
@@ -1540,91 +1639,1260 @@
         <v>777</v>
       </c>
       <c r="V3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="W3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="Z3" s="1">
         <v>3002</v>
       </c>
       <c r="AA3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="AC3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AB3" s="1">
-        <v>9123356789</v>
-      </c>
-      <c r="AC3" s="1" t="s">
+      <c r="AD3" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="AE3" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AD3" s="1">
-        <v>9123356789</v>
-      </c>
-      <c r="AE3" s="1" t="s">
+      <c r="AG3" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AG3" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="AH3" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AJ3" s="1">
         <v>2007</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AL3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AM3" s="1">
         <v>2007</v>
       </c>
       <c r="AN3" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AP3" s="1">
         <v>2005</v>
       </c>
       <c r="AQ3" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AR3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AS3" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AT3" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AS3" s="1">
-        <v>2007</v>
-      </c>
-      <c r="AT3" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="AU3" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV3" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW3" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX3" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="1">
+        <v>4</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="2">
+        <v>46241</v>
+      </c>
+      <c r="I4" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O4" s="1">
+        <v>777</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="T4" s="1">
+        <v>3002</v>
+      </c>
+      <c r="U4" s="1">
+        <v>777</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>3002</v>
+      </c>
+      <c r="AA4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="AE4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ4" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AK4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AL4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM4" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AN4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AO4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AP4" s="1">
+        <v>2005</v>
+      </c>
+      <c r="AQ4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AR4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AS4" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AT4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX4" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" s="1">
+        <v>4</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="2">
+        <v>46241</v>
+      </c>
+      <c r="I5" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O5" s="1">
+        <v>777</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="T5" s="1">
+        <v>3002</v>
+      </c>
+      <c r="U5" s="1">
+        <v>777</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>3002</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="AE5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG5" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ5" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AK5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AL5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM5" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AN5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AO5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AP5" s="1">
+        <v>2005</v>
+      </c>
+      <c r="AQ5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AR5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AS5" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AT5" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX5" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F6" s="1">
+        <v>4</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" s="2">
+        <v>46241</v>
+      </c>
+      <c r="I6" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O6" s="1">
+        <v>777</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="T6" s="1">
+        <v>3002</v>
+      </c>
+      <c r="U6" s="1">
+        <v>777</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="W6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>3002</v>
+      </c>
+      <c r="AA6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="AE6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ6" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AK6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AL6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM6" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AN6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AO6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AP6" s="1">
+        <v>2005</v>
+      </c>
+      <c r="AQ6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AR6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AS6" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AT6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX6" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7" s="1">
+        <v>4</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="2">
+        <v>46241</v>
+      </c>
+      <c r="I7" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O7" s="1">
+        <v>777</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="T7" s="1">
+        <v>3002</v>
+      </c>
+      <c r="U7" s="1">
+        <v>777</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>3002</v>
+      </c>
+      <c r="AA7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="AE7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ7" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AK7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AL7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM7" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AN7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AO7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AP7" s="1">
+        <v>2005</v>
+      </c>
+      <c r="AQ7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AR7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AS7" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AT7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX7" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F8" s="1">
+        <v>4</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="2">
+        <v>46241</v>
+      </c>
+      <c r="I8" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O8" s="1">
+        <v>777</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="T8" s="1">
+        <v>3002</v>
+      </c>
+      <c r="U8" s="1">
+        <v>777</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="W8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>3002</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="AE8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ8" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AK8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AL8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM8" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AN8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AO8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AP8" s="1">
+        <v>2005</v>
+      </c>
+      <c r="AQ8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AR8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AS8" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AT8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX8" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" s="1">
+        <v>4</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="2">
+        <v>46241</v>
+      </c>
+      <c r="I9" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O9" s="1">
+        <v>777</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="T9" s="1">
+        <v>3002</v>
+      </c>
+      <c r="U9" s="1">
+        <v>777</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>3002</v>
+      </c>
+      <c r="AA9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="AC9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="AE9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ9" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AK9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AL9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM9" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AN9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AO9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AP9" s="1">
+        <v>2005</v>
+      </c>
+      <c r="AQ9" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AR9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AS9" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AT9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX9" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F10" s="1">
+        <v>4</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" s="2">
+        <v>46241</v>
+      </c>
+      <c r="I10" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O10" s="1">
+        <v>777</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="T10" s="1">
+        <v>3002</v>
+      </c>
+      <c r="U10" s="1">
+        <v>777</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>3002</v>
+      </c>
+      <c r="AA10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="AC10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="AE10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ10" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AK10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AL10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM10" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AN10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AO10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AP10" s="1">
+        <v>2005</v>
+      </c>
+      <c r="AQ10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AR10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AS10" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AT10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX10" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F11" s="1">
+        <v>4</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="2">
+        <v>46241</v>
+      </c>
+      <c r="I11" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O11" s="1">
+        <v>777</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="T11" s="1">
+        <v>3002</v>
+      </c>
+      <c r="U11" s="1">
+        <v>777</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>3002</v>
+      </c>
+      <c r="AA11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB11" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="AC11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>9123356789</v>
+      </c>
+      <c r="AE11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG11" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ11" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AK11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AL11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM11" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AN11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AO11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AP11" s="1">
+        <v>2005</v>
+      </c>
+      <c r="AQ11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="AR11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AS11" s="1">
+        <v>2007</v>
+      </c>
+      <c r="AT11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AW11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX11" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/fileTemplates/studentTemplates/blockApplicantTemplate(XLSX).xlsx
+++ b/fileTemplates/studentTemplates/blockApplicantTemplate(XLSX).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Programming\VSCode\CAPSTONE-preEnrollment\preEnrollmentV9.1\fileTemplates\studentTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A274CC0E-D577-4123-88DC-6522A8E994D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E014557-8665-4BF6-B7E1-AA8E6A6E6491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6741A616-476E-4690-9F1F-0845B32B7F60}"/>
   </bookViews>
@@ -226,36 +226,6 @@
     <t>kanto</t>
   </si>
   <si>
-    <t>A-201736341</t>
-  </si>
-  <si>
-    <t>A-201736342</t>
-  </si>
-  <si>
-    <t>A-201736343</t>
-  </si>
-  <si>
-    <t>A-201736344</t>
-  </si>
-  <si>
-    <t>A-201736345</t>
-  </si>
-  <si>
-    <t>A-201736346</t>
-  </si>
-  <si>
-    <t>A-201736347</t>
-  </si>
-  <si>
-    <t>A-201736348</t>
-  </si>
-  <si>
-    <t>A-201736349</t>
-  </si>
-  <si>
-    <t>A-201736350</t>
-  </si>
-  <si>
     <t>Dave</t>
   </si>
   <si>
@@ -344,6 +314,36 @@
   </si>
   <si>
     <t>Chutek</t>
+  </si>
+  <si>
+    <t>A-201736381</t>
+  </si>
+  <si>
+    <t>A-201736382</t>
+  </si>
+  <si>
+    <t>A-201736383</t>
+  </si>
+  <si>
+    <t>A-201736384</t>
+  </si>
+  <si>
+    <t>A-201736385</t>
+  </si>
+  <si>
+    <t>A-201736386</t>
+  </si>
+  <si>
+    <t>A-201736387</t>
+  </si>
+  <si>
+    <t>A-201736388</t>
+  </si>
+  <si>
+    <t>A-201736389</t>
+  </si>
+  <si>
+    <t>A-201736390</t>
   </si>
 </sst>
 </file>
@@ -1433,16 +1433,16 @@
     </row>
     <row r="2" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="C2" s="1" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F2" s="1">
         <v>4</v>
@@ -1579,16 +1579,16 @@
     </row>
     <row r="3" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="F3" s="1">
         <v>4</v>
@@ -1725,16 +1725,16 @@
     </row>
     <row r="4" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="F4" s="1">
         <v>4</v>
@@ -1871,16 +1871,16 @@
     </row>
     <row r="5" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F5" s="1">
         <v>4</v>
@@ -2017,16 +2017,16 @@
     </row>
     <row r="6" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F6" s="1">
         <v>4</v>
@@ -2163,16 +2163,16 @@
     </row>
     <row r="7" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F7" s="1">
         <v>4</v>
@@ -2309,16 +2309,16 @@
     </row>
     <row r="8" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="F8" s="1">
         <v>4</v>
@@ -2455,16 +2455,16 @@
     </row>
     <row r="9" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F9" s="1">
         <v>4</v>
@@ -2601,16 +2601,16 @@
     </row>
     <row r="10" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="F10" s="1">
         <v>4</v>
@@ -2747,16 +2747,16 @@
     </row>
     <row r="11" spans="1:50" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F11" s="1">
         <v>4</v>
